--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573615124</v>
+        <v>46157.93114693918</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114693918</v>
+        <v>46157.93181397354</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181397354</v>
+        <v>46157.93404976973</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404976973</v>
+        <v>46157.93723055778</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723055778</v>
+        <v>46158.2822090344</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822090344</v>
+        <v>46158.29698272282</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29698272282</v>
+        <v>46158.29820546039</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820546039</v>
+        <v>46158.33391893846</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391893846</v>
+        <v>46158.36861702543</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Дмитриев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861702543</v>
+        <v>46158.37292335256</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
